--- a/data/trans_dic/P44A$otras-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44A$otras-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,24</t>
+          <t>0,0; 60,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,42; 77,04</t>
+          <t>35,03; 78,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 63,91</t>
+          <t>7,81; 59,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,63; 86,47</t>
+          <t>35,55; 86,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 46,33</t>
+          <t>5,46; 47,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,6; 73,91</t>
+          <t>42,4; 74,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,94; 52,51</t>
+          <t>8,91; 51,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,86</t>
+          <t>0,0; 67,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,53; 69,61</t>
+          <t>22,21; 69,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,12</t>
+          <t>0,0; 79,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,93</t>
+          <t>0,0; 10,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,69; 51,32</t>
+          <t>20,23; 50,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 56,41</t>
+          <t>7,43; 55,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,45</t>
+          <t>0,0; 50,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,59</t>
+          <t>0,0; 28,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,68</t>
+          <t>1,0; 9,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 70,46</t>
+          <t>8,82; 71,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 57,53</t>
+          <t>6,82; 54,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,53; 49,55</t>
+          <t>9,77; 51,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 34,63</t>
+          <t>6,12; 35,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,67</t>
+          <t>0,51; 4,81</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,32</t>
+          <t>0,0; 45,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 33,13</t>
+          <t>3,28; 32,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 60,72</t>
+          <t>7,28; 55,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,02</t>
+          <t>0,0; 33,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 39,86</t>
+          <t>7,0; 41,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,76; 25,64</t>
+          <t>4,34; 23,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,34</t>
+          <t>0,0; 20,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,69</t>
+          <t>0,0; 83,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,59</t>
+          <t>0,0; 11,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,02</t>
+          <t>0,0; 49,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,47</t>
+          <t>0,0; 11,9</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,24</t>
+          <t>0,0; 45,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,86; 70,73</t>
+          <t>10,02; 72,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,49</t>
+          <t>0,0; 82,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,13; 73,02</t>
+          <t>11,16; 75,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,21</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 46,86</t>
+          <t>6,26; 46,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,65; 62,01</t>
+          <t>16,27; 62,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,87</t>
+          <t>0,0; 29,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 23,08</t>
+          <t>2,85; 23,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,27; 62,11</t>
+          <t>15,74; 60,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 28,07</t>
+          <t>3,08; 29,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,27; 39,89</t>
+          <t>9,48; 41,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 19,43</t>
+          <t>4,37; 20,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,18; 44,06</t>
+          <t>10,54; 43,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,09; 47,1</t>
+          <t>10,8; 47,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,13; 64,68</t>
+          <t>14,0; 64,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,26; 72,41</t>
+          <t>15,55; 72,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,13; 43,02</t>
+          <t>15,46; 45,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,12; 50,63</t>
+          <t>18,01; 48,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,37; 24,91</t>
+          <t>9,85; 25,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,66; 30,06</t>
+          <t>16,52; 30,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,05</t>
+          <t>0,07; 1,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,06; 44,39</t>
+          <t>26,28; 46,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,96; 34,86</t>
+          <t>18,11; 35,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,24</t>
+          <t>0,12; 1,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,96; 31,91</t>
+          <t>19,3; 32,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,62; 30,37</t>
+          <t>19,07; 29,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,89</t>
+          <t>0,17; 0,85</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3911</t>
+          <t>0; 4174</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8279; 18006</t>
+          <t>8187; 18233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1480</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>817; 7075</t>
+          <t>865; 6574</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4993; 13650</t>
+          <t>5612; 13638</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 897</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>991; 8350</t>
+          <t>984; 8563</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15899; 28941</t>
+          <t>16602; 29346</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1231</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2155; 12662</t>
+          <t>2150; 12477</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6231</t>
+          <t>0; 6260</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1929</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4599; 14210</t>
+          <t>4533; 14141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4456</t>
+          <t>0; 4550</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3925</t>
+          <t>0; 4257</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9210; 22853</t>
+          <t>9009; 22651</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1116; 8474</t>
+          <t>1116; 8360</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3808</t>
+          <t>0; 4618</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4651</t>
+          <t>0; 4629</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6389</t>
+          <t>0; 5993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>583; 4929</t>
+          <t>569; 5627</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1174; 9380</t>
+          <t>1174; 9572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1402; 11478</t>
+          <t>1360; 10956</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1028</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2147; 11163</t>
+          <t>2202; 11541</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3174; 14145</t>
+          <t>2499; 14315</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>583; 5251</t>
+          <t>577; 5419</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4949</t>
+          <t>0; 5004</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1004; 8622</t>
+          <t>855; 8487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1383</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1013; 8308</t>
+          <t>996; 7613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7764</t>
+          <t>0; 6928</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1087; 9806</t>
+          <t>1722; 10311</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2676; 11909</t>
+          <t>2018; 11127</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1099</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1664</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1320</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>0; 2639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5363</t>
+          <t>0; 5452</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1446</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1894</t>
+          <t>0; 1669</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5663</t>
+          <t>0; 6329</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1618</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2808</t>
+          <t>0; 3189</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4184</t>
+          <t>0; 4215</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1024; 7347</t>
+          <t>1041; 7494</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1147</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5190</t>
+          <t>0; 5180</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>957; 6283</t>
+          <t>960; 6457</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>0; 1711</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>974; 7282</t>
+          <t>973; 7287</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2971; 11775</t>
+          <t>3090; 11819</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1522</t>
+          <t>0; 2104</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5319</t>
+          <t>0; 4601</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1137; 9304</t>
+          <t>1150; 9619</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5246</t>
+          <t>0; 5114</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2936; 12776</t>
+          <t>3239; 12399</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>895; 7916</t>
+          <t>867; 8281</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2820</t>
+          <t>0; 2462</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3362; 14472</t>
+          <t>3438; 14968</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3044; 13316</t>
+          <t>2991; 13946</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5928</t>
+          <t>0; 5686</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2200; 11857</t>
+          <t>2836; 11742</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2928; 12437</t>
+          <t>2851; 12545</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3756</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2125; 9731</t>
+          <t>2107; 9704</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2055; 9754</t>
+          <t>2095; 9713</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 1062</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6348; 18047</t>
+          <t>6486; 19165</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7226; 20188</t>
+          <t>7183; 19287</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 2277</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10251; 27241</t>
+          <t>10773; 27710</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26601; 47997</t>
+          <t>26384; 47921</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>509; 8172</t>
+          <t>516; 8265</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26798; 47477</t>
+          <t>28103; 50006</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>20859; 40485</t>
+          <t>21031; 40709</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>747; 5927</t>
+          <t>594; 5537</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41016; 69024</t>
+          <t>41755; 70122</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>54103; 83751</t>
+          <t>52593; 82205</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2053; 11182</t>
+          <t>2137; 10686</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$otras-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44A$otras-Provincia-trans_dic.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,01</t>
+          <t>0,0; 63,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,03; 78,01</t>
+          <t>35,39; 77,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 59,38</t>
+          <t>7,39; 59,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,55; 86,4</t>
+          <t>33,81; 86,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 47,51</t>
+          <t>5,73; 51,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,4; 74,94</t>
+          <t>42,51; 75,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 51,74</t>
+          <t>9,04; 52,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,18</t>
+          <t>0,0; 67,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,21; 69,28</t>
+          <t>21,79; 65,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,76</t>
+          <t>0,0; 78,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,77</t>
+          <t>0,0; 9,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,23; 50,87</t>
+          <t>18,75; 50,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 55,65</t>
+          <t>7,27; 55,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,21</t>
+          <t>0,0; 50,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,69</t>
+          <t>0,0; 29,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,91</t>
+          <t>1,02; 8,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 71,91</t>
+          <t>8,82; 67,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 54,91</t>
+          <t>6,78; 54,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 51,22</t>
+          <t>9,86; 53,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 35,05</t>
+          <t>7,17; 35,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,81</t>
+          <t>0,51; 4,49</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,83</t>
+          <t>0,0; 45,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 32,61</t>
+          <t>3,91; 30,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 55,64</t>
+          <t>7,16; 55,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,93</t>
+          <t>0,0; 32,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 41,91</t>
+          <t>4,58; 42,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 23,96</t>
+          <t>4,23; 24,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,5</t>
+          <t>0,0; 19,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,04</t>
+          <t>0,0; 83,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,97</t>
+          <t>0,0; 11,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,2</t>
+          <t>0,0; 42,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,9</t>
+          <t>0,0; 10,7</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,58</t>
+          <t>0,0; 47,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,02; 72,15</t>
+          <t>9,93; 76,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,32</t>
+          <t>0,0; 82,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,16; 75,04</t>
+          <t>11,32; 75,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,26; 46,89</t>
+          <t>6,39; 52,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,27; 62,24</t>
+          <t>15,9; 63,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,3</t>
+          <t>0,0; 35,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 23,86</t>
+          <t>2,29; 22,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,74; 60,27</t>
+          <t>15,15; 62,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 29,37</t>
+          <t>3,11; 29,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,48; 41,26</t>
+          <t>9,12; 42,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 20,35</t>
+          <t>4,84; 20,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,54; 43,64</t>
+          <t>8,06; 43,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,8; 47,51</t>
+          <t>10,8; 47,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,0; 64,5</t>
+          <t>14,03; 64,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,55; 72,11</t>
+          <t>15,34; 65,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,46; 45,68</t>
+          <t>15,68; 45,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,01; 48,37</t>
+          <t>17,57; 48,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,85; 25,34</t>
+          <t>9,48; 25,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,52; 30,01</t>
+          <t>16,79; 30,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,06</t>
+          <t>0,2; 1,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,28; 46,76</t>
+          <t>25,5; 44,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,11; 35,06</t>
+          <t>18,16; 35,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,16</t>
+          <t>0,12; 1,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,3; 32,42</t>
+          <t>19,54; 32,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,07; 29,8</t>
+          <t>19,02; 29,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,85</t>
+          <t>0,27; 1,11</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4174</t>
+          <t>0; 4393</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8187; 18233</t>
+          <t>8272; 18067</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>865; 6574</t>
+          <t>818; 6541</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5612; 13638</t>
+          <t>5337; 13668</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>984; 8563</t>
+          <t>1034; 9338</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16602; 29346</t>
+          <t>16647; 29400</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>723</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>723</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2150; 12477</t>
+          <t>2180; 12721</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6260</t>
+          <t>0; 6248</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,32 +2039,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4533; 14141</t>
+          <t>4448; 13368</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4550</t>
+          <t>0; 4458</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4257</t>
+          <t>0; 3958</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9009; 22651</t>
+          <t>8351; 22283</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1116; 8360</t>
+          <t>1093; 8325</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4618</t>
+          <t>0; 3644</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1831</t>
         </is>
       </c>
     </row>
@@ -2187,27 +2187,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4629</t>
+          <t>0; 4656</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5993</t>
+          <t>0; 6066</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>569; 5627</t>
+          <t>567; 5002</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1174; 9572</t>
+          <t>1174; 9039</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1360; 10956</t>
+          <t>1353; 10917</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,17 +2217,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2202; 11541</t>
+          <t>2222; 12055</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2499; 14315</t>
+          <t>2929; 14573</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>577; 5419</t>
+          <t>571; 5064</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5004</t>
+          <t>0; 4929</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>855; 8487</t>
+          <t>1016; 7871</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>996; 7613</t>
+          <t>979; 7592</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6928</t>
+          <t>0; 6732</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1722; 10311</t>
+          <t>1126; 10541</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2018; 11127</t>
+          <t>1967; 11443</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>432</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>952</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2639</t>
+          <t>0; 2674</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5452</t>
+          <t>0; 5476</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2538,12 +2538,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1669</t>
+          <t>0; 1738</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6329</t>
+          <t>0; 5455</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3189</t>
+          <t>0; 3024</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>375</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>375</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4215</t>
+          <t>0; 4360</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1041; 7494</t>
+          <t>1032; 7974</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2691,32 +2691,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5180</t>
+          <t>0; 5190</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>960; 6457</t>
+          <t>974; 6472</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1711</t>
+          <t>0; 1562</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>973; 7287</t>
+          <t>994; 8157</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3090; 11819</t>
+          <t>3019; 11991</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2104</t>
+          <t>0; 2003</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1784</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4601</t>
+          <t>0; 5581</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1150; 9619</t>
+          <t>925; 8872</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5114</t>
+          <t>0; 6679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3239; 12399</t>
+          <t>3117; 12850</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>867; 8281</t>
+          <t>877; 8362</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2462</t>
+          <t>0; 3333</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3438; 14968</t>
+          <t>3307; 15476</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2991; 13946</t>
+          <t>3313; 13762</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5686</t>
+          <t>0; 6453</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2836; 11742</t>
+          <t>2168; 11699</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2851; 12545</t>
+          <t>2851; 12582</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2107; 9704</t>
+          <t>2111; 9641</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2095; 9713</t>
+          <t>2067; 8850</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6486; 19165</t>
+          <t>6580; 18975</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7183; 19287</t>
+          <t>7006; 19361</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5665</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10773; 27710</t>
+          <t>10363; 27833</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26384; 47921</t>
+          <t>26818; 48850</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>516; 8265</t>
+          <t>1134; 8062</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28103; 50006</t>
+          <t>27274; 47331</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21031; 40709</t>
+          <t>21083; 41399</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>594; 5537</t>
+          <t>656; 5722</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41755; 70122</t>
+          <t>42263; 69254</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>52593; 82205</t>
+          <t>52459; 81742</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2137; 10686</t>
+          <t>2978; 12210</t>
         </is>
       </c>
     </row>
